--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/IOWA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/IOWA_2022.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C101">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C154">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C161">
@@ -8239,7 +8239,7 @@
         <v>25</v>
       </c>
       <c r="D438">
-        <v>0.009708737864077669</v>
+        <v>0.009708737864077667</v>
       </c>
     </row>
     <row r="439">
